--- a/dashboard/autogen/CN264_270__278_286.xlsx
+++ b/dashboard/autogen/CN264_270__278_286.xlsx
@@ -607,31 +607,20 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>emr_db_tong_hop_luot_kham, emr_db_tong_hop_luot_ra</t>
+          <t>emr_db_tong_hop_luot_vao_ra</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT ngay,
-       SUM(so_luot_vao) AS so_luot_vao,
-       SUM(so_luot_ra)  AS so_luot_ra
-FROM (
-    SELECT ngay_vao AS ngay, so_noi_tru AS so_luot_vao, 0 AS so_luot_ra
-    FROM emr_db_tong_hop_luot_kham
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_vao &gt;= :from_date
-      AND ngay_vao &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-    UNION ALL
-    SELECT ngay_ra, 0, so_luot_ra
-    FROM emr_db_tong_hop_luot_ra
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_ra &gt;= :from_date
-      AND ngay_ra &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-) x
-GROUP BY ngay
-ORDER BY ngay
+          <t xml:space="preserve">SELECT ngay_theo_doi AS ngay,
+       so_luot_vao,
+       so_luot_ra
+FROM emr_db_tong_hop_luot_vao_ra
+WHERE ma_csyt = :ma_csyt
+  AND ngay_theo_doi &gt;= :from_date
+  AND ngay_theo_doi &lt; :to_date
+  AND (:thang IS NULL OR thang = :thang)
+ORDER BY ngay_theo_doi
 </t>
         </is>
       </c>
@@ -707,7 +696,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>emr_db_tong_hop_luot_kham</t>
+          <t>emr_db_tong_hop_luot_bhyt</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -715,25 +704,11 @@
           <t xml:space="preserve">SELECT ngay_vao,
        loai,
        luot
-FROM (
-    SELECT ngay_vao,
-           'BHYT' AS loai,
-           so_ho_so_bh AS luot
-    FROM emr_db_tong_hop_luot_kham
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_vao &gt;= :from_date
-      AND ngay_vao &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-    UNION ALL
-    SELECT ngay_vao,
-           'Không BHYT',
-           so_ho_so_khong_bh
-    FROM emr_db_tong_hop_luot_kham
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_vao &gt;= :from_date
-      AND ngay_vao &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-) x
+FROM emr_db_tong_hop_luot_bhyt
+WHERE ma_csyt = :ma_csyt
+  AND ngay_vao &gt;= :from_date
+  AND ngay_vao &lt; :to_date
+  AND (:thang IS NULL OR thang = :thang)
 ORDER BY ngay_vao, loai
 </t>
         </is>
@@ -766,7 +741,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>emr_db_tong_hop_luot_kham</t>
+          <t>emr_db_tong_hop_cap_cuu_tu_vong</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -774,25 +749,11 @@
           <t xml:space="preserve">SELECT ngay_vao,
        loai,
        luot
-FROM (
-    SELECT ngay_vao,
-           'Cấp cứu' AS loai,
-           so_cap_cuu AS luot
-    FROM emr_db_tong_hop_luot_kham
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_vao &gt;= :from_date
-      AND ngay_vao &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-    UNION ALL
-    SELECT ngay_vao,
-           'Tử vong',
-           so_tu_vong
-    FROM emr_db_tong_hop_luot_kham
-    WHERE ma_csyt = :ma_csyt
-      AND ngay_vao &gt;= :from_date
-      AND ngay_vao &lt; :to_date
-      AND (:thang IS NULL OR thang = :thang)
-) x
+FROM emr_db_tong_hop_cap_cuu_tu_vong
+WHERE ma_csyt = :ma_csyt
+  AND ngay_vao &gt;= :from_date
+  AND ngay_vao &lt; :to_date
+  AND (:thang IS NULL OR thang = :thang)
 ORDER BY ngay_vao, loai
 </t>
         </is>

--- a/dashboard/autogen/CN264_270__278_286.xlsx
+++ b/dashboard/autogen/CN264_270__278_286.xlsx
@@ -612,16 +612,16 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT ngay_theo_doi AS ngay,
-       so_luot_vao,
-       so_luot_ra
+          <t>SELECT ngay_theo_doi AS ngay,
+       SUM(so_luot_vao) AS so_luot_vao,
+       SUM(so_luot_ra) AS so_luot_ra
 FROM emr_db_tong_hop_luot_vao_ra
 WHERE ma_csyt = :ma_csyt
   AND ngay_theo_doi &gt;= :from_date
   AND ngay_theo_doi &lt; :to_date
   AND (:thang IS NULL OR thang = :thang)
-ORDER BY ngay_theo_doi
-</t>
+GROUP BY ngay_theo_doi
+ORDER BY ngay_theo_doi</t>
         </is>
       </c>
     </row>
@@ -701,16 +701,16 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT ngay_vao,
+          <t>SELECT ngay_vao,
        loai,
-       luot
+       SUM(luot) AS luot
 FROM emr_db_tong_hop_luot_bhyt
 WHERE ma_csyt = :ma_csyt
   AND ngay_vao &gt;= :from_date
   AND ngay_vao &lt; :to_date
   AND (:thang IS NULL OR thang = :thang)
-ORDER BY ngay_vao, loai
-</t>
+GROUP BY ngay_vao, loai
+ORDER BY ngay_vao, loai</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT ngay_vao,
+          <t>SELECT ngay_vao,
        loai,
-       luot
+       SUM(luot) AS luot
 FROM emr_db_tong_hop_cap_cuu_tu_vong
 WHERE ma_csyt = :ma_csyt
   AND ngay_vao &gt;= :from_date
   AND ngay_vao &lt; :to_date
   AND (:thang IS NULL OR thang = :thang)
-ORDER BY ngay_vao, loai
-</t>
+GROUP BY ngay_vao, loai
+ORDER BY ngay_vao, loai</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       <c r="F10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ten_nhom,
-       COUNT(DISTINCT ma_bn) AS so_ca
+       COUNT(DISTINCT ma_bn, cccd) AS so_ca
 FROM emr_db_tong_hop_benh_nhom
 WHERE ma_csyt = :ma_csyt
   AND ngay_ghi_nhan &gt;= :from_date

--- a/dashboard/autogen/CN264_270__278_286.xlsx
+++ b/dashboard/autogen/CN264_270__278_286.xlsx
@@ -149,12 +149,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -166,6 +160,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,11 +448,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
-    <col width="21.00390625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="21.00390625" customWidth="1" style="16" min="2" max="2"/>
     <col width="85.8515625" customWidth="1" min="3" max="3"/>
     <col width="82.28125" customWidth="1" min="4" max="4"/>
-    <col width="15.28125" customWidth="1" style="1" min="5" max="5"/>
-    <col width="39.421875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="15.28125" customWidth="1" style="16" min="5" max="5"/>
+    <col width="39.421875" customWidth="1" style="16" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5" customFormat="1" customHeight="1" s="2">
@@ -503,7 +503,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Tổng số hồ sơ: Đếm số hồ sơ (mr.medical_record_id) có cùng ngày mr.examination_date
@@ -515,12 +515,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT SUM(so_ho_so)          AS tong_ho_so,
        SUM(so_ho_so_bh)       AS tong_ho_so_bh,
@@ -552,7 +552,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Lượt khám: Đếm số hồ sơ (mr.medical_record_id) có cùng ngày mr.examination_date
@@ -560,12 +560,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ngay_vao,
        SUM(so_ho_so) AS luot_kham
@@ -596,7 +596,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Ngày vào viện:  mr.examination_date
 Ngày ra viện:  mr.finish_examination_date
@@ -605,12 +605,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_vao_ra</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>SELECT ngay_theo_doi AS ngay,
        SUM(so_luot_vao) AS so_luot_vao,
@@ -641,7 +641,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Ngày vào viện: mr.examination_date
  Lượt khám nội trú: Đếm số hồ sơ (mr.medical_record_id) có cùng ngày mr.examination_date và mr.type_of_excamination = 3, 4, 9
@@ -649,12 +649,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ngay_vao,
        SUM(so_noi_tru)   AS luot_noi_tru,
@@ -686,7 +686,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Ngày vào viện: mr.examination_date
 Loại: mr.is_health_insurance (null coi như 0)
@@ -694,12 +694,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_bhyt</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>SELECT ngay_vao,
        loai,
@@ -730,7 +730,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Ngày vào viện: mr.examination_date
 Loai:  mr.reason_code = 2 --&gt; Cấp cứu; mr.treatment_result_Id = 5, 8 --&gt; Tử vong
@@ -739,12 +739,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_cap_cuu_tu_vong</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>SELECT ngay_vao,
        loai,
@@ -760,23 +760,23 @@
       </c>
     </row>
     <row r="8" ht="71.25" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>CN_270</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Biểu đồ theo dõi tình hình tai nạn thương tích tại bệnh viện theo ngày</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>medical_records (mr)
  cats_accidents (ca) (mr.accident_id = ca.accident_id) với ca.accident_type = 1</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Ngày vào viện: mr.examination_date
 Tên tai nạn: ca.name_vi
@@ -784,12 +784,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_tai_nan</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ngay_vao,
        ten_tai_nan AS loai,
@@ -804,7 +804,7 @@
 </t>
         </is>
       </c>
-      <c r="G8" s="1" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9" ht="171" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -817,12 +817,12 @@
           <t>Biểu đồ theo dõi lượt điều trị nội trú, ngoại trú tại bệnh viện theo tháng</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Năm vào viện: YEAR(mr.examination_date)
  Tháng vào viện: MONTH(mr.examination_date)
@@ -832,12 +832,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT nam,
        thang,
@@ -853,7 +853,7 @@
 </t>
         </is>
       </c>
-      <c r="G9" s="1" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
     <row r="10" ht="156.75" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -866,7 +866,7 @@
           <t>Biểu đồ thống kê nhóm bệnh phổ biến tại bệnh viện theo tháng</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>medical_records (mr)
  medical_records_diagnoses_discharge (mrd) (mr.medical_records_id = mrd.medical_records_id)
@@ -874,7 +874,7 @@
  cats_diseases_groups (cg) (cgd.diseases_group_id = cg.diseases_group_id)</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Mã bệnh: mrd.diseases_code
@@ -886,12 +886,12 @@
  Cơ sở khám chữa bệnh: mrd.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_benh_nhom</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ten_nhom,
        COUNT(DISTINCT ma_bn, cccd) AS so_ca
@@ -906,7 +906,7 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="1" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
     <row r="11" ht="156.75" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -919,13 +919,13 @@
           <t>Biểu đồ thống kê tai nạn thương tích tại bệnh viện theo tháng</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>medical_records (mr)
  cats_accidents (ca) (mr.accident_id = ca.accident_id)</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Lượt: Đếm số hồ sơ (mr.medical_record_id) có cùng Năm, Tháng của mr.examination_date và có mr.accident_id thuộc ca.accident_type = 1
@@ -933,12 +933,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT nam,
        thang,
@@ -953,7 +953,7 @@
 </t>
         </is>
       </c>
-      <c r="G11" s="1" t="n"/>
+      <c r="G11" s="16" t="n"/>
     </row>
     <row r="12" ht="156.75" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -971,7 +971,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Lượt khám tử vong: Đếm số hồ sơ (mr.medical_record_id) có cùng Năm, Tháng của mr.examination_date và mr.treatment_result_Id = 5, 8
@@ -979,12 +979,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT nam,
        thang,
@@ -999,7 +999,7 @@
 </t>
         </is>
       </c>
-      <c r="G12" s="1" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13" ht="156.75" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -1017,7 +1017,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Lượt khám cấp cứu: Đếm số hồ sơ (mr.medical_record_id) có cùng Năm, Tháng của mr.examination_date và mr.reason_code = 2
@@ -1025,12 +1025,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT nam,
        thang,
@@ -1045,7 +1045,7 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="1" t="n"/>
+      <c r="G13" s="16" t="n"/>
     </row>
     <row r="14" ht="171" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -1063,7 +1063,7 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Số ngày điều trị: Tổng mr.treatment_day_number của các hồ sơ có cùng Năm, Tháng của mr.examination_date và mr.type_of_excamination = 3, 4, 9
@@ -1071,12 +1071,12 @@
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_luot_kham</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT nam,
        thang,
@@ -1091,7 +1091,7 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="1" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="15" ht="156.75" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -1104,14 +1104,14 @@
           <t>Biểu đồ thống kê sử dụng dịch vụ theo nhóm chi phí tại bệnh viện theo tháng</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>medical_records_services (mrs)
  medical_records (mr) (mrs.medical_record_id = mr.medical_record_id)
  cats_cost_groups (ccg) (mrs.cost_group_id = ccg.cost_group_id)</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
  Nhóm dịch vụ: ccg.name_vi
@@ -1121,12 +1121,12 @@
  Cơ sở khám chữa bệnh: mrs.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>emr_db_tong_hop_nhom_dich_vu</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">SELECT ten_nhom,
        COUNT(DISTINCT ma_hs) AS so_luot
@@ -1141,9 +1141,9 @@
 </t>
         </is>
       </c>
-      <c r="G15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="171" customHeight="1">
+      <c r="G15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="342" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>CN_285</t>
@@ -1156,40 +1156,60 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>medical_records (mr)</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
+          <t xml:space="preserve"> medical_records (mr) full join với cats_cost_groups (ccg) (18 bản ghi code_vi: 1-&gt;18 )</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
- Số ngày điều trị: Tổng mr.treatment_day_number của các hồ sơ có cùng Năm, Tháng của mr.examination_date và mr.type_of_excamination = 3, 4, 9
+ Nhóm dịch vu: ccg.name_vi
+Tiền dịch vụ:
+        = mr.test_money  nếu ccg.code_vi = 1
+        = mr.radiology_money  nếu ccg.code_vi = 2
+        = mr.func_exploration_money  nếu ccg.code_vi = 3
+        = mr.drug_ins_money  nếu ccg.code_vi = 4
+        = mr.drug_out_ins_money  nếu ccg.code_vi = 5
+        = mr.drug_radio_money  nếu ccg.code_vi = 6
+        = mr.blood_money  nếu ccg.code_vi = 7
+        = mr.surgery_money  nếu ccg.code_vi = 8
+        = mr.service_money  nếu ccg.code_vi = 9
+        = mr.material_ins_money  nếu ccg.code_vi = 10
+        = mr.material_radio_money  nếu ccg.code_vi = 11
+        = mr.transfer_money  nếu ccg.code_vi = 12
+        = mr.examinal_money  nếu ccg.code_vi = 13
+        = mr.bed_out_money  nếu ccg.code_vi = 14
+        = mr.bed_in_money  nếu ccg.code_vi = 15
+        = mr.bed_temporary_money  nếu ccg.code_vi = 16
+        = mr.blood_product_money  nếu ccg.code_vi = 17
+        = mr.tricks_money  nếu ccg.code_vi = 18
  Thời gian vào viện: mr.examination_date (Tháng/Năm)
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>emr_db_tong_hop_luot_kham</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SELECT nam,
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>emr_db_tong_hop_nhom_chi_phi</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>SELECT nam,
        thang,
-       SUM(so_ngay_dieu_tri) AS so_ngay_dieu_tri
-FROM emr_db_tong_hop_luot_kham
+       ma_nhom,
+       ten_nhom,
+       SUM(tien_dich_vu) AS tien_dich_vu
+FROM emr_db_tong_hop_nhom_chi_phi
 WHERE ma_csyt = :ma_csyt
   AND ngay_vao &gt;= :from_date
   AND ngay_vao &lt; :to_date
   AND (:thang IS NULL OR thang = :thang)
-GROUP BY nam, thang
-ORDER BY nam, thang
-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="n"/>
-    </row>
-    <row r="17" ht="299.25" customHeight="1">
+GROUP BY nam, thang, ma_nhom, ten_nhom
+ORDER BY nam, thang, CAST(ma_nhom AS UNSIGNED)</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="156.75" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>CN_286</t>
@@ -1205,41 +1225,40 @@
           <t>medical_records (mr)</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
- Tiền của bệnh nhân: Tổng (mr.patient_money + mr.patient_pay_together_money) của các hồ sơ có cùng Năm, Tháng của mr.examination_date
- Tiền bảo hiểm thanh toán: Tổng mr.insurance_money của các hồ sơ có cùng Năm, Tháng của mr.examination_date
+Tiền chi không bảo hiểm: Tổng (mr.patient_money + mr.external_capacity_money +  mr.other_souces_money) của các hồ sơ có cùng Năm, Tháng của mr.examination_date
+ Tiền chi bảo hiểm: Tổng mr.insurance_money + mr.patient_pay_together_money của các hồ sơ có cùng Năm, Tháng của mr.examination_date
  Tỉ lệ % tiền của bệnh nhân: Tiền của bệnh nhân / (Tiền của bệnh nhân + Tiền bảo hiểm thanh toán) × 100, làm tròn 2 chữ số thập phân
  Tỉ lệ % tiền bảo hiểm thanh toán: Tiền bảo hiểm thanh toán / (Tiền của bệnh nhân + Tiền bảo hiểm thanh toán) × 100, làm tròn 2 chữ số thập phân
  Thời gian vào viện: mr.examination_date (Tháng/Năm)
  Cơ sở khám chữa bệnh: mr.healthfacilities_id</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>emr_db_tong_hop_luot_kham</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SELECT nam,
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>emr_db_tong_hop_chi_phi_bh</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>SELECT nam,
        thang,
-       SUM(tien_benh_nhan) AS tien_benh_nhan,
-       SUM(tien_bao_hiem)  AS tien_bao_hiem,
-       ROUND(SUM(tien_benh_nhan) / NULLIF(SUM(tien_benh_nhan) + SUM(tien_bao_hiem), 0) * 100, 2) AS ty_le_benh_nhan,
-       ROUND(SUM(tien_bao_hiem) / NULLIF(SUM(tien_benh_nhan) + SUM(tien_bao_hiem), 0) * 100, 2) AS ty_le_bao_hiem
-FROM emr_db_tong_hop_luot_kham
+       SUM(tien_khong_bh) AS tien_khong_bh,
+       SUM(tien_bao_hiem) AS tien_bao_hiem,
+       ROUND(SUM(tien_khong_bh) / NULLIF(SUM(tien_khong_bh) + SUM(tien_bao_hiem), 0) * 100, 2) AS ty_le_benh_nhan,
+       ROUND(SUM(tien_bao_hiem) / NULLIF(SUM(tien_khong_bh) + SUM(tien_bao_hiem), 0) * 100, 2) AS ty_le_bao_hiem
+FROM emr_db_tong_hop_chi_phi_bh
 WHERE ma_csyt = :ma_csyt
   AND ngay_vao &gt;= :from_date
   AND ngay_vao &lt; :to_date
   AND (:thang IS NULL OR thang = :thang)
 GROUP BY nam, thang
-ORDER BY nam, thang
-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="n"/>
+ORDER BY nam, thang</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
